--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/16.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/16.xlsx
@@ -426,13 +426,13 @@
         <v>-8.611879315476283</v>
       </c>
       <c r="E2">
-        <v>-12.62136179669974</v>
+        <v>-24.99033607482238</v>
       </c>
       <c r="F2">
-        <v>-1.052836892122818</v>
+        <v>-2.792711620471204</v>
       </c>
       <c r="G2">
-        <v>-12.53517989184079</v>
+        <v>-16.24856916505819</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.84638252643146</v>
       </c>
       <c r="E3">
-        <v>-13.43076312693471</v>
+        <v>-24.89294671281343</v>
       </c>
       <c r="F3">
-        <v>-1.21948701785062</v>
+        <v>-2.728684618806622</v>
       </c>
       <c r="G3">
-        <v>-12.54270807239709</v>
+        <v>-16.46083803449072</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.943181701112984</v>
       </c>
       <c r="E4">
-        <v>-13.79751517986791</v>
+        <v>-25.03239654140563</v>
       </c>
       <c r="F4">
-        <v>-1.030486711227884</v>
+        <v>-2.918930790003168</v>
       </c>
       <c r="G4">
-        <v>-11.83062627962756</v>
+        <v>-16.23803004333392</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.870763128858147</v>
       </c>
       <c r="E5">
-        <v>-14.56717462221157</v>
+        <v>-25.91478781569623</v>
       </c>
       <c r="F5">
-        <v>-0.6806721272300699</v>
+        <v>-2.649417313665335</v>
       </c>
       <c r="G5">
-        <v>-13.50660982215683</v>
+        <v>-15.5734777528717</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.641162532553528</v>
       </c>
       <c r="E6">
-        <v>-14.92339797307694</v>
+        <v>-25.92071105969826</v>
       </c>
       <c r="F6">
-        <v>-0.8544064509866131</v>
+        <v>-2.655022047512676</v>
       </c>
       <c r="G6">
-        <v>-12.20221846368305</v>
+        <v>-15.49081012021056</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.271079884408243</v>
       </c>
       <c r="E7">
-        <v>-15.67946746492358</v>
+        <v>-26.83462051308225</v>
       </c>
       <c r="F7">
-        <v>-0.3590816773804402</v>
+        <v>-2.624152107879949</v>
       </c>
       <c r="G7">
-        <v>-11.43505581423112</v>
+        <v>-15.6652295224926</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.786103649404957</v>
       </c>
       <c r="E8">
-        <v>-15.69749531994811</v>
+        <v>-26.8413815247757</v>
       </c>
       <c r="F8">
-        <v>-0.4331534621713692</v>
+        <v>-2.422551504693231</v>
       </c>
       <c r="G8">
-        <v>-11.76593490924466</v>
+        <v>-15.24428703608319</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.204643521545076</v>
       </c>
       <c r="E9">
-        <v>-15.82985808671831</v>
+        <v>-27.46113942051745</v>
       </c>
       <c r="F9">
-        <v>-0.3539292321350273</v>
+        <v>-2.589065778166974</v>
       </c>
       <c r="G9">
-        <v>-11.25866994789875</v>
+        <v>-15.65144110032154</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.551289859405707</v>
       </c>
       <c r="E10">
-        <v>-17.21048112828082</v>
+        <v>-27.39444405533248</v>
       </c>
       <c r="F10">
-        <v>-0.06136394771208953</v>
+        <v>-2.450291872278181</v>
       </c>
       <c r="G10">
-        <v>-10.07184930370665</v>
+        <v>-14.75620503086459</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.853097250389876</v>
       </c>
       <c r="E11">
-        <v>-17.63723999028966</v>
+        <v>-27.99131957191347</v>
       </c>
       <c r="F11">
-        <v>0.2345595381617974</v>
+        <v>-2.408447721293167</v>
       </c>
       <c r="G11">
-        <v>-10.65554151937217</v>
+        <v>-14.61525193343904</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.129411199152521</v>
       </c>
       <c r="E12">
-        <v>-19.11979898176483</v>
+        <v>-28.80900348110847</v>
       </c>
       <c r="F12">
-        <v>0.1683415047168106</v>
+        <v>-2.287539215180551</v>
       </c>
       <c r="G12">
-        <v>-10.09428156028075</v>
+        <v>-14.43948844966806</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.392307908847307</v>
       </c>
       <c r="E13">
-        <v>-19.00463988774978</v>
+        <v>-29.72690025585621</v>
       </c>
       <c r="F13">
-        <v>0.03018721764531183</v>
+        <v>-2.221946599124678</v>
       </c>
       <c r="G13">
-        <v>-10.01405379968205</v>
+        <v>-13.76461718875993</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.662304941497943</v>
       </c>
       <c r="E14">
-        <v>-20.24412397991522</v>
+        <v>-29.90375301551476</v>
       </c>
       <c r="F14">
-        <v>0.4361733952269607</v>
+        <v>-2.216954857155408</v>
       </c>
       <c r="G14">
-        <v>-8.649407201847996</v>
+        <v>-14.00730169533451</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.948339837518544</v>
       </c>
       <c r="E15">
-        <v>-21.15002256277964</v>
+        <v>-30.89071128311648</v>
       </c>
       <c r="F15">
-        <v>0.6278882618286699</v>
+        <v>-1.807861473445858</v>
       </c>
       <c r="G15">
-        <v>-8.576515610164323</v>
+        <v>-12.95432475202237</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.254301495303123</v>
       </c>
       <c r="E16">
-        <v>-21.79121372599969</v>
+        <v>-31.17875392932237</v>
       </c>
       <c r="F16">
-        <v>0.9434962422952815</v>
+        <v>-1.859724728167732</v>
       </c>
       <c r="G16">
-        <v>-8.647434116706592</v>
+        <v>-13.04329235284475</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.587250512353001</v>
       </c>
       <c r="E17">
-        <v>-21.71368172251437</v>
+        <v>-32.6109336474622</v>
       </c>
       <c r="F17">
-        <v>1.155748821914599</v>
+        <v>-1.692363863208328</v>
       </c>
       <c r="G17">
-        <v>-6.704786130989023</v>
+        <v>-12.83800542395454</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9474134577651868</v>
       </c>
       <c r="E18">
-        <v>-22.54429442500127</v>
+        <v>-32.14814851048533</v>
       </c>
       <c r="F18">
-        <v>1.132927299967472</v>
+        <v>-1.694016456176914</v>
       </c>
       <c r="G18">
-        <v>-6.898919831957425</v>
+        <v>-12.52197743623018</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3337949016844392</v>
       </c>
       <c r="E19">
-        <v>-23.62173160327623</v>
+        <v>-33.90902072176091</v>
       </c>
       <c r="F19">
-        <v>1.45072382711228</v>
+        <v>-1.555388342951013</v>
       </c>
       <c r="G19">
-        <v>-7.157360880026169</v>
+        <v>-11.69456285796351</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2509882001286732</v>
       </c>
       <c r="E20">
-        <v>-24.85134815057897</v>
+        <v>-34.42596640786952</v>
       </c>
       <c r="F20">
-        <v>1.580459416269128</v>
+        <v>-1.126461358516235</v>
       </c>
       <c r="G20">
-        <v>-6.524089934364523</v>
+        <v>-11.63602248119258</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.8010324761170381</v>
       </c>
       <c r="E21">
-        <v>-25.36649829674353</v>
+        <v>-34.25660147998264</v>
       </c>
       <c r="F21">
-        <v>1.465912771810012</v>
+        <v>-0.9929335033893716</v>
       </c>
       <c r="G21">
-        <v>-6.051039461166985</v>
+        <v>-11.62771301188901</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.310623605785714</v>
       </c>
       <c r="E22">
-        <v>-25.97593127174779</v>
+        <v>-35.21282273025729</v>
       </c>
       <c r="F22">
-        <v>1.702106826105041</v>
+        <v>-1.084405973843507</v>
       </c>
       <c r="G22">
-        <v>-5.756930595458132</v>
+        <v>-11.52882370608544</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.773998077928936</v>
       </c>
       <c r="E23">
-        <v>-26.410578735478</v>
+        <v>-35.86404219916734</v>
       </c>
       <c r="F23">
-        <v>2.05219808481539</v>
+        <v>-0.9856596092253891</v>
       </c>
       <c r="G23">
-        <v>-6.110059867041111</v>
+        <v>-11.01634132496964</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.183287086274724</v>
       </c>
       <c r="E24">
-        <v>-27.04914338377361</v>
+        <v>-35.89481997276047</v>
       </c>
       <c r="F24">
-        <v>1.958261221337926</v>
+        <v>-0.8426618579497216</v>
       </c>
       <c r="G24">
-        <v>-5.696609145187072</v>
+        <v>-10.94150975359995</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.533956116435298</v>
       </c>
       <c r="E25">
-        <v>-26.78917727641527</v>
+        <v>-35.87383955268293</v>
       </c>
       <c r="F25">
-        <v>1.827998790512898</v>
+        <v>-0.8135604827219722</v>
       </c>
       <c r="G25">
-        <v>-5.026680528769076</v>
+        <v>-11.55741357736258</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.823429175515431</v>
       </c>
       <c r="E26">
-        <v>-27.51165454807301</v>
+        <v>-35.22620889942397</v>
       </c>
       <c r="F26">
-        <v>2.110428999762584</v>
+        <v>-0.5891035661572097</v>
       </c>
       <c r="G26">
-        <v>-5.095582913077927</v>
+        <v>-10.7937534850912</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.048520506839545</v>
       </c>
       <c r="E27">
-        <v>-27.26703091065266</v>
+        <v>-36.19566235074904</v>
       </c>
       <c r="F27">
-        <v>2.01513692721414</v>
+        <v>-0.6966513344300723</v>
       </c>
       <c r="G27">
-        <v>-5.133458864592729</v>
+        <v>-11.25028433604778</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.208515816873632</v>
       </c>
       <c r="E28">
-        <v>-27.48807478391507</v>
+        <v>-36.40260455595156</v>
       </c>
       <c r="F28">
-        <v>2.332890379254003</v>
+        <v>-0.8557326671984951</v>
       </c>
       <c r="G28">
-        <v>-5.215874895792885</v>
+        <v>-11.60993869288866</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.302318070433153</v>
       </c>
       <c r="E29">
-        <v>-27.10437265277115</v>
+        <v>-35.86651701021253</v>
       </c>
       <c r="F29">
-        <v>2.24061687752136</v>
+        <v>-0.8722602536191507</v>
       </c>
       <c r="G29">
-        <v>-5.389681847150162</v>
+        <v>-11.07547759993764</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.329974427178397</v>
       </c>
       <c r="E30">
-        <v>-27.0173761386098</v>
+        <v>-36.05777258145248</v>
       </c>
       <c r="F30">
-        <v>2.230640020522043</v>
+        <v>-0.5850172297591998</v>
       </c>
       <c r="G30">
-        <v>-5.730284014412539</v>
+        <v>-11.19767976742876</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.291565467004746</v>
       </c>
       <c r="E31">
-        <v>-26.91753234368868</v>
+        <v>-36.41295438329609</v>
       </c>
       <c r="F31">
-        <v>2.271092514270354</v>
+        <v>-0.6414638413207637</v>
       </c>
       <c r="G31">
-        <v>-5.097724836041835</v>
+        <v>-11.42946761336083</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.18688174799974</v>
       </c>
       <c r="E32">
-        <v>-26.19582038413824</v>
+        <v>-35.66571541576441</v>
       </c>
       <c r="F32">
-        <v>2.006946030335259</v>
+        <v>-0.7766293788029618</v>
       </c>
       <c r="G32">
-        <v>-5.537984355672893</v>
+        <v>-11.59592846416646</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.016730960254755</v>
       </c>
       <c r="E33">
-        <v>-26.05830874242132</v>
+        <v>-35.04025390701</v>
       </c>
       <c r="F33">
-        <v>2.087955392124634</v>
+        <v>-0.7782571207494628</v>
       </c>
       <c r="G33">
-        <v>-5.592740778892439</v>
+        <v>-11.39577950195321</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.783432851279338</v>
       </c>
       <c r="E34">
-        <v>-26.44492721082618</v>
+        <v>-34.89687562721614</v>
       </c>
       <c r="F34">
-        <v>2.213666772438681</v>
+        <v>-0.5423455397387889</v>
       </c>
       <c r="G34">
-        <v>-6.347747105124165</v>
+        <v>-12.01296450683953</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.491305848669395</v>
       </c>
       <c r="E35">
-        <v>-26.50337169636918</v>
+        <v>-34.71197350500896</v>
       </c>
       <c r="F35">
-        <v>2.309132802141713</v>
+        <v>-0.5924070953595741</v>
       </c>
       <c r="G35">
-        <v>-6.251655210301279</v>
+        <v>-11.85294928819886</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.145770288407404</v>
       </c>
       <c r="E36">
-        <v>-25.55052642346724</v>
+        <v>-34.89780849286172</v>
       </c>
       <c r="F36">
-        <v>2.158953105483774</v>
+        <v>-0.7641773600040797</v>
       </c>
       <c r="G36">
-        <v>-6.221555730258226</v>
+        <v>-12.14770039974233</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.754344378122773</v>
       </c>
       <c r="E37">
-        <v>-25.36355931711255</v>
+        <v>-34.30942160080811</v>
       </c>
       <c r="F37">
-        <v>2.607002123044776</v>
+        <v>-0.4980519063436965</v>
       </c>
       <c r="G37">
-        <v>-6.448556527340512</v>
+        <v>-11.88390619953659</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.32470409214768</v>
       </c>
       <c r="E38">
-        <v>-24.43188466019648</v>
+        <v>-33.44739713836701</v>
       </c>
       <c r="F38">
-        <v>2.389280661832176</v>
+        <v>-0.6768848314644705</v>
       </c>
       <c r="G38">
-        <v>-6.998073981404136</v>
+        <v>-11.98310338607531</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.864656491535952</v>
       </c>
       <c r="E39">
-        <v>-23.73061423231666</v>
+        <v>-33.42912474574606</v>
       </c>
       <c r="F39">
-        <v>2.253494677165282</v>
+        <v>-0.4797483002114386</v>
       </c>
       <c r="G39">
-        <v>-7.11897179395278</v>
+        <v>-12.29259966745069</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.383628064967465</v>
       </c>
       <c r="E40">
-        <v>-23.82806699296173</v>
+        <v>-32.79183486288361</v>
       </c>
       <c r="F40">
-        <v>2.065722011033495</v>
+        <v>-0.6433823402256473</v>
       </c>
       <c r="G40">
-        <v>-6.845305546948928</v>
+        <v>-11.72170602083999</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1102021472171121</v>
       </c>
       <c r="E41">
-        <v>-23.93115317527234</v>
+        <v>-32.48750782414614</v>
       </c>
       <c r="F41">
-        <v>2.570043683001473</v>
+        <v>-0.5226163133063131</v>
       </c>
       <c r="G41">
-        <v>-6.823042128197329</v>
+        <v>-11.35766188061404</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.6066785659827093</v>
       </c>
       <c r="E42">
-        <v>-21.75342361040568</v>
+        <v>-32.17418270755543</v>
       </c>
       <c r="F42">
-        <v>2.597159461564712</v>
+        <v>-0.4957954335384707</v>
       </c>
       <c r="G42">
-        <v>-6.716697473839321</v>
+        <v>-11.60095056174954</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.098215369809795</v>
       </c>
       <c r="E43">
-        <v>-21.31127699371877</v>
+        <v>-31.07143815228859</v>
       </c>
       <c r="F43">
-        <v>2.523343642301248</v>
+        <v>-0.2806187169872711</v>
       </c>
       <c r="G43">
-        <v>-7.16707733118393</v>
+        <v>-12.42920270803764</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.578247031828699</v>
       </c>
       <c r="E44">
-        <v>-20.25136500985349</v>
+        <v>-30.44639552737989</v>
       </c>
       <c r="F44">
-        <v>2.160046550455469</v>
+        <v>-0.4719343105008309</v>
       </c>
       <c r="G44">
-        <v>-8.145522307497686</v>
+        <v>-12.01660941747827</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.039111180799491</v>
       </c>
       <c r="E45">
-        <v>-20.58799818216168</v>
+        <v>-30.62973532605443</v>
       </c>
       <c r="F45">
-        <v>2.262830377794832</v>
+        <v>-0.4436132573665186</v>
       </c>
       <c r="G45">
-        <v>-6.836870276914865</v>
+        <v>-12.06123557134765</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.478451207779772</v>
       </c>
       <c r="E46">
-        <v>-20.24025666311267</v>
+        <v>-30.34521583262651</v>
       </c>
       <c r="F46">
-        <v>2.191789589330746</v>
+        <v>-0.4039551679574923</v>
       </c>
       <c r="G46">
-        <v>-7.957599189960957</v>
+        <v>-12.3304590662378</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.89504984516956</v>
       </c>
       <c r="E47">
-        <v>-19.60849378277659</v>
+        <v>-29.33223242490272</v>
       </c>
       <c r="F47">
-        <v>2.356000173057303</v>
+        <v>-0.413810254948598</v>
       </c>
       <c r="G47">
-        <v>-7.094265192593199</v>
+        <v>-12.43097384990115</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.286665908316687</v>
       </c>
       <c r="E48">
-        <v>-19.23905634475683</v>
+        <v>-28.5375622206147</v>
       </c>
       <c r="F48">
-        <v>2.241910787404533</v>
+        <v>-0.403947712650867</v>
       </c>
       <c r="G48">
-        <v>-7.512195082561873</v>
+        <v>-12.45626972836672</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.652949174398784</v>
       </c>
       <c r="E49">
-        <v>-18.29623711330788</v>
+        <v>-28.77816457311623</v>
       </c>
       <c r="F49">
-        <v>2.106461119903175</v>
+        <v>-0.4493041414237512</v>
       </c>
       <c r="G49">
-        <v>-7.705047602406577</v>
+        <v>-11.8929439888588</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.995692153040943</v>
       </c>
       <c r="E50">
-        <v>-17.3325642590536</v>
+        <v>-28.24401747848949</v>
       </c>
       <c r="F50">
-        <v>2.125528480780814</v>
+        <v>-0.3308277220057547</v>
       </c>
       <c r="G50">
-        <v>-7.810902296024772</v>
+        <v>-12.40411870448658</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.314453750226594</v>
       </c>
       <c r="E51">
-        <v>-17.46766222412443</v>
+        <v>-26.95909014965707</v>
       </c>
       <c r="F51">
-        <v>2.287124736984135</v>
+        <v>-0.4343471395988033</v>
       </c>
       <c r="G51">
-        <v>-7.839800048037071</v>
+        <v>-12.64261040513568</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.606178563893518</v>
       </c>
       <c r="E52">
-        <v>-16.34830496196046</v>
+        <v>-26.99609683924776</v>
       </c>
       <c r="F52">
-        <v>2.129289268789524</v>
+        <v>-0.5583106646929438</v>
       </c>
       <c r="G52">
-        <v>-7.645338603060281</v>
+        <v>-12.74083429128585</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.873590032853559</v>
       </c>
       <c r="E53">
-        <v>-16.73250522524522</v>
+        <v>-26.54703071427712</v>
       </c>
       <c r="F53">
-        <v>1.967263918271551</v>
+        <v>-0.5031264850532463</v>
       </c>
       <c r="G53">
-        <v>-7.399666329136505</v>
+        <v>-12.50655029401717</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.117012144527574</v>
       </c>
       <c r="E54">
-        <v>-15.86229554603525</v>
+        <v>-26.42380640805441</v>
       </c>
       <c r="F54">
-        <v>2.103573431137016</v>
+        <v>-0.3840445290638033</v>
       </c>
       <c r="G54">
-        <v>-8.546124802113814</v>
+        <v>-12.59837820618547</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.330999242258667</v>
       </c>
       <c r="E55">
-        <v>-15.17061189762967</v>
+        <v>-25.73986645020194</v>
       </c>
       <c r="F55">
-        <v>2.150591564919916</v>
+        <v>-0.5543038515656026</v>
       </c>
       <c r="G55">
-        <v>-8.094404173825801</v>
+        <v>-13.17997484652464</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.518845770043677</v>
       </c>
       <c r="E56">
-        <v>-13.99778241438313</v>
+        <v>-26.12645774776276</v>
       </c>
       <c r="F56">
-        <v>2.000604049499426</v>
+        <v>-0.3315169236848839</v>
       </c>
       <c r="G56">
-        <v>-8.355596285237679</v>
+        <v>-12.87040904369293</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.680641520053243</v>
       </c>
       <c r="E57">
-        <v>-14.74349075770021</v>
+        <v>-25.817239957097</v>
       </c>
       <c r="F57">
-        <v>2.067620629120711</v>
+        <v>-0.5084330066355799</v>
       </c>
       <c r="G57">
-        <v>-8.196796036809918</v>
+        <v>-13.34471090310431</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.810365033953257</v>
       </c>
       <c r="E58">
-        <v>-13.90786503448683</v>
+        <v>-25.07189389170053</v>
       </c>
       <c r="F58">
-        <v>2.07721312364513</v>
+        <v>-0.6132057441090641</v>
       </c>
       <c r="G58">
-        <v>-8.090696362821816</v>
+        <v>-12.85041334863573</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.908085503455665</v>
       </c>
       <c r="E59">
-        <v>-13.05548848591907</v>
+        <v>-24.76886652500326</v>
       </c>
       <c r="F59">
-        <v>2.022009063187765</v>
+        <v>-0.4932606292859041</v>
       </c>
       <c r="G59">
-        <v>-7.879566321054797</v>
+        <v>-13.02174401192963</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.974746704983086</v>
       </c>
       <c r="E60">
-        <v>-13.93427962337357</v>
+        <v>-24.13089510680266</v>
       </c>
       <c r="F60">
-        <v>1.83653594496615</v>
+        <v>-0.7124789503953626</v>
       </c>
       <c r="G60">
-        <v>-8.83476464659179</v>
+        <v>-13.68261828629772</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.005592432431087</v>
       </c>
       <c r="E61">
-        <v>-13.02169701287383</v>
+        <v>-23.98045467179384</v>
       </c>
       <c r="F61">
-        <v>1.674359831580869</v>
+        <v>-0.6741445920960099</v>
       </c>
       <c r="G61">
-        <v>-8.485525266017454</v>
+        <v>-12.9808389112464</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.995642215923008</v>
       </c>
       <c r="E62">
-        <v>-12.08951516686889</v>
+        <v>-23.96458237039696</v>
       </c>
       <c r="F62">
-        <v>1.523487619774189</v>
+        <v>-0.7372579045153042</v>
       </c>
       <c r="G62">
-        <v>-8.143655159813537</v>
+        <v>-13.11653817290112</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.945478707957876</v>
       </c>
       <c r="E63">
-        <v>-12.75191317386687</v>
+        <v>-23.43545282497071</v>
       </c>
       <c r="F63">
-        <v>1.247290046863167</v>
+        <v>-0.8289126157980554</v>
       </c>
       <c r="G63">
-        <v>-8.300323416914008</v>
+        <v>-12.8230384475715</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.84984452897505</v>
       </c>
       <c r="E64">
-        <v>-12.24622300990433</v>
+        <v>-23.96240417439927</v>
       </c>
       <c r="F64">
-        <v>1.409215993292803</v>
+        <v>-0.5379071471945891</v>
       </c>
       <c r="G64">
-        <v>-7.839657694578882</v>
+        <v>-13.40171518674502</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.700775889329215</v>
       </c>
       <c r="E65">
-        <v>-10.75505538934058</v>
+        <v>-23.52910619592334</v>
       </c>
       <c r="F65">
-        <v>1.430056060412433</v>
+        <v>-0.6387915280793325</v>
       </c>
       <c r="G65">
-        <v>-7.814769013214641</v>
+        <v>-13.13465678863755</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.499083758536919</v>
       </c>
       <c r="E66">
-        <v>-12.50000775024219</v>
+        <v>-23.02177672437003</v>
       </c>
       <c r="F66">
-        <v>1.310000772724701</v>
+        <v>-0.9736532520892131</v>
       </c>
       <c r="G66">
-        <v>-7.343863773526551</v>
+        <v>-13.5200489817735</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.241463776593812</v>
       </c>
       <c r="E67">
-        <v>-12.2207639290332</v>
+        <v>-23.28864422611605</v>
       </c>
       <c r="F67">
-        <v>1.236324119184907</v>
+        <v>-1.035736903826828</v>
       </c>
       <c r="G67">
-        <v>-7.969282105169046</v>
+        <v>-13.63162429808356</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.923463767020405</v>
       </c>
       <c r="E68">
-        <v>-11.19450756399293</v>
+        <v>-23.31394933887091</v>
       </c>
       <c r="F68">
-        <v>0.8258631008933349</v>
+        <v>-1.175489111618327</v>
       </c>
       <c r="G68">
-        <v>-7.739801709477845</v>
+        <v>-12.91540928920824</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.54705319355743</v>
       </c>
       <c r="E69">
-        <v>-10.92839178893218</v>
+        <v>-23.03509043795258</v>
       </c>
       <c r="F69">
-        <v>1.152617593132017</v>
+        <v>-1.085614561884191</v>
       </c>
       <c r="G69">
-        <v>-8.485048547459799</v>
+        <v>-13.49936303797136</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.114045542771924</v>
       </c>
       <c r="E70">
-        <v>-11.81619911813595</v>
+        <v>-23.34162284353178</v>
       </c>
       <c r="F70">
-        <v>1.060198298736482</v>
+        <v>-1.411424715283682</v>
       </c>
       <c r="G70">
-        <v>-7.396660353786848</v>
+        <v>-12.85317103306994</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.626111976345851</v>
       </c>
       <c r="E71">
-        <v>-11.27733788206722</v>
+        <v>-22.90666744356906</v>
       </c>
       <c r="F71">
-        <v>0.9910113965198611</v>
+        <v>-1.399562494075593</v>
       </c>
       <c r="G71">
-        <v>-7.305951406010817</v>
+        <v>-12.676020430718</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.086776163830091</v>
       </c>
       <c r="E72">
-        <v>-11.08312068882626</v>
+        <v>-22.91638102031551</v>
       </c>
       <c r="F72">
-        <v>0.6858656963506073</v>
+        <v>-1.475460828989695</v>
       </c>
       <c r="G72">
-        <v>-7.466291058114338</v>
+        <v>-13.21813219441028</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.501361397309449</v>
       </c>
       <c r="E73">
-        <v>-11.23786317414236</v>
+        <v>-23.07667994323902</v>
       </c>
       <c r="F73">
-        <v>0.5081278729363342</v>
+        <v>-1.560943374754187</v>
       </c>
       <c r="G73">
-        <v>-7.331531991392765</v>
+        <v>-12.8236542090418</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.873700869942802</v>
       </c>
       <c r="E74">
-        <v>-11.21820506847506</v>
+        <v>-23.16997556474505</v>
       </c>
       <c r="F74">
-        <v>0.6421701442203361</v>
+        <v>-1.653396632213237</v>
       </c>
       <c r="G74">
-        <v>-6.097824090727965</v>
+        <v>-12.86338737660413</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.206897838971969</v>
       </c>
       <c r="E75">
-        <v>-12.10388401489523</v>
+        <v>-22.65730702233668</v>
       </c>
       <c r="F75">
-        <v>0.1448042733336654</v>
+        <v>-1.475760697989508</v>
       </c>
       <c r="G75">
-        <v>-6.597345686057515</v>
+        <v>-12.50306760010986</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.5072343652996129</v>
       </c>
       <c r="E76">
-        <v>-11.89058383218594</v>
+        <v>-23.25241643405469</v>
       </c>
       <c r="F76">
-        <v>0.2281893928342693</v>
+        <v>-1.834634307904338</v>
       </c>
       <c r="G76">
-        <v>-6.505646885165243</v>
+        <v>-12.45852089933342</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.2205737183744534</v>
       </c>
       <c r="E77">
-        <v>-12.54469473174988</v>
+        <v>-23.57021568296498</v>
       </c>
       <c r="F77">
-        <v>0.4590686418729363</v>
+        <v>-1.812594764785454</v>
       </c>
       <c r="G77">
-        <v>-5.965872366623694</v>
+        <v>-12.73519312168693</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.9690252537303259</v>
       </c>
       <c r="E78">
-        <v>-12.89267173144729</v>
+        <v>-24.03079771733711</v>
       </c>
       <c r="F78">
-        <v>-0.08854433893274691</v>
+        <v>-1.712157702298223</v>
       </c>
       <c r="G78">
-        <v>-5.987609408634548</v>
+        <v>-11.82956690505499</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.730309916613182</v>
       </c>
       <c r="E79">
-        <v>-13.22582250724358</v>
+        <v>-23.59677065454596</v>
       </c>
       <c r="F79">
-        <v>-0.03388534422642433</v>
+        <v>-2.107365163234645</v>
       </c>
       <c r="G79">
-        <v>-5.61581197075562</v>
+        <v>-11.80972680563814</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.496493211624226</v>
       </c>
       <c r="E80">
-        <v>-13.54656526425885</v>
+        <v>-24.6226511562436</v>
       </c>
       <c r="F80">
-        <v>0.3045864049248564</v>
+        <v>-1.922886914263792</v>
       </c>
       <c r="G80">
-        <v>-5.005863818418138</v>
+        <v>-11.85924263526901</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.253160177389893</v>
       </c>
       <c r="E81">
-        <v>-14.32971050219735</v>
+        <v>-25.17484421979091</v>
       </c>
       <c r="F81">
-        <v>0.2522302715983165</v>
+        <v>-1.910415843014645</v>
       </c>
       <c r="G81">
-        <v>-5.316793566012028</v>
+        <v>-11.55321249507325</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.991423820980498</v>
       </c>
       <c r="E82">
-        <v>-14.97583317361176</v>
+        <v>-24.76238627869828</v>
       </c>
       <c r="F82">
-        <v>0.0411382347103213</v>
+        <v>-2.098971316342077</v>
       </c>
       <c r="G82">
-        <v>-4.954835069475813</v>
+        <v>-11.55458968201758</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.699194431529966</v>
       </c>
       <c r="E83">
-        <v>-15.42157992713477</v>
+        <v>-26.04952350284644</v>
       </c>
       <c r="F83">
-        <v>0.1071930797769567</v>
+        <v>-2.036495018455536</v>
       </c>
       <c r="G83">
-        <v>-4.67113124839689</v>
+        <v>-11.90371981458912</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.35971706660517</v>
       </c>
       <c r="E84">
-        <v>-16.54432901633049</v>
+        <v>-26.83720174326662</v>
       </c>
       <c r="F84">
-        <v>0.2125912346395546</v>
+        <v>-1.93749765851437</v>
       </c>
       <c r="G84">
-        <v>-4.238823659151162</v>
+        <v>-11.9198355502743</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.960349939193788</v>
       </c>
       <c r="E85">
-        <v>-17.5915069312862</v>
+        <v>-27.57466826388974</v>
       </c>
       <c r="F85">
-        <v>0.1124399589062887</v>
+        <v>-2.069055655957376</v>
       </c>
       <c r="G85">
-        <v>-4.713075860379456</v>
+        <v>-11.3736418839321</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.489082524041459</v>
       </c>
       <c r="E86">
-        <v>-19.32516980648669</v>
+        <v>-27.99802624191883</v>
       </c>
       <c r="F86">
-        <v>-0.1281204199688961</v>
+        <v>-2.295065761402387</v>
       </c>
       <c r="G86">
-        <v>-4.352219775507818</v>
+        <v>-11.31080110850565</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.932394128879213</v>
       </c>
       <c r="E87">
-        <v>-19.86405368492546</v>
+        <v>-28.72370061622598</v>
       </c>
       <c r="F87">
-        <v>0.06076060174783598</v>
+        <v>-2.227200933560635</v>
       </c>
       <c r="G87">
-        <v>-4.01702703965661</v>
+        <v>-11.40766767098473</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>7.278322347432887</v>
       </c>
       <c r="E88">
-        <v>-21.45344390671557</v>
+        <v>-29.65791121858635</v>
       </c>
       <c r="F88">
-        <v>0.1824601987301253</v>
+        <v>-2.317254410653775</v>
       </c>
       <c r="G88">
-        <v>-3.810323197275596</v>
+        <v>-11.58903921889924</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>7.521345007644104</v>
       </c>
       <c r="E89">
-        <v>-22.20080967151947</v>
+        <v>-31.43356663325997</v>
       </c>
       <c r="F89">
-        <v>-0.07227354640695902</v>
+        <v>-2.207378929979046</v>
       </c>
       <c r="G89">
-        <v>-3.442226949309572</v>
+        <v>-11.17778338873774</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>7.654665783480587</v>
       </c>
       <c r="E90">
-        <v>-24.13159249179984</v>
+        <v>-32.30447596170412</v>
       </c>
       <c r="F90">
-        <v>0.1102646661065372</v>
+        <v>-2.489930909236943</v>
       </c>
       <c r="G90">
-        <v>-4.309361452956413</v>
+        <v>-11.71319460825853</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>7.671480653104319</v>
       </c>
       <c r="E91">
-        <v>-26.08487729942433</v>
+        <v>-33.36469361756492</v>
       </c>
       <c r="F91">
-        <v>0.1191000328247968</v>
+        <v>-2.44109202390269</v>
       </c>
       <c r="G91">
-        <v>-4.326377657028267</v>
+        <v>-10.7109964677005</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>7.575331910709928</v>
       </c>
       <c r="E92">
-        <v>-27.37364477421525</v>
+        <v>-35.09729682984761</v>
       </c>
       <c r="F92">
-        <v>-0.2145083713046481</v>
+        <v>-2.676621727540673</v>
       </c>
       <c r="G92">
-        <v>-3.759724819253375</v>
+        <v>-11.33835146848347</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>7.370030336234331</v>
       </c>
       <c r="E93">
-        <v>-28.62512479402701</v>
+        <v>-36.34854363324798</v>
       </c>
       <c r="F93">
-        <v>0.2052618398595845</v>
+        <v>-2.494814963443849</v>
       </c>
       <c r="G93">
-        <v>-4.182663564622965</v>
+        <v>-11.71496906066758</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.058266237496992</v>
       </c>
       <c r="E94">
-        <v>-31.46166128600355</v>
+        <v>-37.07639393931583</v>
       </c>
       <c r="F94">
-        <v>0.282215514844853</v>
+        <v>-2.695084380214269</v>
       </c>
       <c r="G94">
-        <v>-4.448149453599279</v>
+        <v>-11.12529137866705</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.655457685292572</v>
       </c>
       <c r="E95">
-        <v>-32.75395191357244</v>
+        <v>-38.9460174538856</v>
       </c>
       <c r="F95">
-        <v>0.04497771762229701</v>
+        <v>-2.586723983519259</v>
       </c>
       <c r="G95">
-        <v>-4.623194548988243</v>
+        <v>-11.62408134343243</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.169293691680034</v>
       </c>
       <c r="E96">
-        <v>-34.68886470214781</v>
+        <v>-41.01328848075716</v>
       </c>
       <c r="F96">
-        <v>0.06403762319331083</v>
+        <v>-2.920769765637383</v>
       </c>
       <c r="G96">
-        <v>-4.292239311427302</v>
+        <v>-11.35143143390913</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.618934787175176</v>
       </c>
       <c r="E97">
-        <v>-36.83347300812236</v>
+        <v>-42.00745834321609</v>
       </c>
       <c r="F97">
-        <v>0.1795973609860503</v>
+        <v>-2.7432953630572</v>
       </c>
       <c r="G97">
-        <v>-4.928347394616104</v>
+        <v>-11.84590444729129</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.998627973897167</v>
       </c>
       <c r="E98">
-        <v>-39.16524993754494</v>
+        <v>-43.88275603571748</v>
       </c>
       <c r="F98">
-        <v>-0.05556454752509019</v>
+        <v>-2.615236389523619</v>
       </c>
       <c r="G98">
-        <v>-5.238495853462725</v>
+        <v>-12.03333429354267</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.351944675923308</v>
       </c>
       <c r="E99">
-        <v>-41.43373464999932</v>
+        <v>-45.44961257084543</v>
       </c>
       <c r="F99">
-        <v>0.2003620466720255</v>
+        <v>-3.214910604860445</v>
       </c>
       <c r="G99">
-        <v>-5.258799429255076</v>
+        <v>-12.49489717371894</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.642601106823447</v>
       </c>
       <c r="E100">
-        <v>-43.5863357125974</v>
+        <v>-47.14619630087112</v>
       </c>
       <c r="F100">
-        <v>0.1927137304419776</v>
+        <v>-3.254074987297403</v>
       </c>
       <c r="G100">
-        <v>-5.247947460977344</v>
+        <v>-12.4076775409413</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.941587805692757</v>
       </c>
       <c r="E101">
-        <v>-46.17672247141302</v>
+        <v>-49.35386021104697</v>
       </c>
       <c r="F101">
-        <v>0.08454634335182099</v>
+        <v>-3.293627874046273</v>
       </c>
       <c r="G101">
-        <v>-5.761499148302327</v>
+        <v>-13.0226941384994</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.143113908647922</v>
       </c>
       <c r="E102">
-        <v>-47.68271858011489</v>
+        <v>-51.20203574059793</v>
       </c>
       <c r="F102">
-        <v>0.08478242806161884</v>
+        <v>-3.135915004227276</v>
       </c>
       <c r="G102">
-        <v>-6.028233112946945</v>
+        <v>-12.41261687488589</v>
       </c>
     </row>
   </sheetData>
